--- a/BART_FANG_2024_6-2FTNO_Example.xlsx
+++ b/BART_FANG_2024_6-2FTNO_Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/stephanie_rich_chem_uzh_ch/Documents/Documents/enviPath-PFAS/BART/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\strich\Documents\BART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{0CEB8B98-C94E-4F6F-9864-DAF7FDE43A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872E1295-79A4-4C6C-A567-C95E3B2F7350}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29208657-1433-49BF-A4AC-BEFDBEB90314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="15720" tabRatio="857" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="15" r:id="rId1"/>
@@ -24,6 +24,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="AcidityWaterSediment">#REF!</definedName>
@@ -101,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="218">
   <si>
     <t>pH</t>
   </si>
@@ -160,15 +161,9 @@
     <t>Initial amount of sludge in bioreactor</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
     <t>Reactant_SMILES</t>
   </si>
   <si>
-    <t>Product_SMILES</t>
-  </si>
-  <si>
     <t>Biological treatment technology</t>
   </si>
   <si>
@@ -749,6 +744,18 @@
   </si>
   <si>
     <t>Test General Scenario</t>
+  </si>
+  <si>
+    <t>Product_1</t>
+  </si>
+  <si>
+    <t>Product_1_SMILES</t>
+  </si>
+  <si>
+    <t>Product_2</t>
+  </si>
+  <si>
+    <t>Product_2_SMILES</t>
   </si>
 </sst>
 </file>
@@ -816,7 +823,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,6 +870,17 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1049,7 +1067,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1134,6 +1152,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1149,8 +1170,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1723,8 +1746,131 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Description"/>
+      <sheetName val="Compounds"/>
+      <sheetName val="Connectivity"/>
+      <sheetName val="Scenario_Sludge"/>
+      <sheetName val="Scenario_Soil"/>
+      <sheetName val="Scenario_Water-Sediment"/>
+      <sheetName val="Scenario_General"/>
+      <sheetName val="Kinetics_Confidence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>6:2 FTAA</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCN(C)C)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>OH-6:2 FTAA</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCN(C)CO)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>6:2 FTUAA</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC/C=[N+](C)\C)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>6:2 FTSAm-SeAm</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCNC)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>6:2 FTSAm-PrA</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>6:2 FTSAm-AcAL</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC=O)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>6:2 FTSAm-AcA</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC(O)=O)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>6:2 FTSAm-ForAL</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>6:2 FTSAm</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>6:2 FTSI</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>FC(F)(C(F)(C(F)(C(F)(C(F)(C(F)(F)F)F)F)F)F)CCS(O)=O</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>6:2 FTSA</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(O)(=O)=O)F</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>6:2 FTSAm-PrAm</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>C(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)F)CS(NCCCN)(=O)=O</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2036,58 +2182,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2133,10 +2279,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2144,10 +2290,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2155,10 +2301,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2166,10 +2312,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2177,10 +2323,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2188,10 +2334,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2199,10 +2345,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2210,10 +2356,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2221,10 +2367,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2232,10 +2378,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2243,10 +2389,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2254,10 +2400,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2265,10 +2411,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2276,10 +2422,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2287,10 +2433,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2298,10 +2444,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2309,10 +2455,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2340,437 +2486,530 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
     <col min="2" max="2" width="73.77734375" customWidth="1"/>
     <col min="3" max="3" width="19.109375" customWidth="1"/>
     <col min="4" max="4" width="72.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="72.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" t="str">
         <f>_xlfn.XLOOKUP(A2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>C[N+](C)(CCCNS(=O)(=O)CCC(C(C(C(C(C(F)(F)F)(F)F)(F)F)(F)F)(F)F)(F)F)[O-]</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN(C)C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="61"/>
+      <c r="F2">
+        <f>_xlfn.XLOOKUP(E2,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(A3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>C[N+](C)(CCCNS(=O)(=O)CCC(C(C(C(C(C(F)(F)F)(F)F)(F)F)(F)F)(F)F)(F)F)[O-]</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCC/C=[N+](\C)/C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="61"/>
+      <c r="F3">
+        <f>_xlfn.XLOOKUP(E3,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(A4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>C[N+](C)(CCCNS(=O)(=O)CCC(C(C(C(C(C(F)(F)F)(F)F)(F)F)(F)F)(F)F)(F)F)[O-]</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="61"/>
+      <c r="F4">
+        <f>_xlfn.XLOOKUP(E4,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(A5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCC/C=[N+](\C)/C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCNC)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="61"/>
+      <c r="F5">
+        <f>_xlfn.XLOOKUP(E5,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(A6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN(C)C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCNC)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="62"/>
+      <c r="F6">
+        <f>_xlfn.XLOOKUP(E6,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(A7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCNC)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(C7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="62"/>
+      <c r="F7">
+        <f>_xlfn.XLOOKUP(E7,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(A8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(C8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="62"/>
+      <c r="F8">
+        <f>_xlfn.XLOOKUP(E8,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(A9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(C9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="61"/>
+      <c r="F9">
+        <f>_xlfn.XLOOKUP(E9,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(A10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(C10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N(C)CCC(O)=O)(=O)=O)F</v>
       </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E10" s="61"/>
+      <c r="F10">
+        <f>_xlfn.XLOOKUP(E10,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(A11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(C11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="62"/>
+      <c r="F11">
+        <f>_xlfn.XLOOKUP(E11,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(A12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(C12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC)(=O)=O)F</v>
       </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" s="62"/>
+      <c r="F12">
+        <f>_xlfn.XLOOKUP(E12,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(A13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC)(=O)=O)F</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(C13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCCO)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="62"/>
+      <c r="F13">
+        <f>_xlfn.XLOOKUP(E13,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(A14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCCO)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(C14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E14" s="62"/>
+      <c r="F14">
+        <f>_xlfn.XLOOKUP(E14,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(A15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(C15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC(O)=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E15" s="62"/>
+      <c r="F15">
+        <f>_xlfn.XLOOKUP(E15,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(A16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC(O)=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(C16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
       </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E16" s="62"/>
+      <c r="F16">
+        <f>_xlfn.XLOOKUP(E16,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(A17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(C17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="62"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(A18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)C(C)CC)=O)(=O)=O)F</v>
       </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="62"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(A19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)C(C)CC)=O)(=O)=O)F</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)CCC)=O)(=O)=O)F</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="62"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(A20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)CCC)=O)(=O)=O)F</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="62"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(A21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(C21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
       </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="62"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(A22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)C(C)CC)=O)(=O)=O)F</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" s="62"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(A23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCC=O)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E23" s="62"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="C24" s="9"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E24" s="62"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="C25" s="9"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E25" s="62"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
-      <c r="E26" s="10"/>
+      <c r="E26" s="62"/>
+      <c r="G26" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
       <formula1>"multistep reaction, "</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="E1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comment" prompt="Use this column to take note of confusing entries or data that shoudl be included in future versions of this template." sqref="F1" xr:uid="{CB5F148A-FFF9-4AAA-8D3A-53806F4B9DE0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="G1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comment" prompt="Use this column to take note of confusing entries or data that shoudl be included in future versions of this template." sqref="H1" xr:uid="{CB5F148A-FFF9-4AAA-8D3A-53806F4B9DE0}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2812,13 +3051,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -2830,13 +3069,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2844,17 +3083,17 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>197</v>
+        <v>91</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>195</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="42"/>
@@ -2862,83 +3101,83 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>92</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G3" s="27"/>
       <c r="H3" s="44"/>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="44"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="27"/>
       <c r="H5" s="44"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="56"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="28"/>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="54" t="s">
-        <v>198</v>
+      <c r="C7" s="55" t="s">
+        <v>196</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F7" s="41">
         <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="26" t="s">
         <v>18</v>
       </c>
@@ -2947,28 +3186,28 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H8" s="44"/>
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="27"/>
       <c r="F9" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="44"/>
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="28"/>
@@ -2977,326 +3216,326 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="55"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" t="s">
         <v>163</v>
-      </c>
-      <c r="E13" t="s">
-        <v>165</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" t="s">
         <v>163</v>
-      </c>
-      <c r="E14" t="s">
-        <v>165</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H15" s="44"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
         <v>1</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G20" s="27"/>
       <c r="H20" s="44"/>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G21" s="27"/>
       <c r="H21" s="44"/>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="55"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" s="32"/>
       <c r="F26" s="28"/>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="55"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="28"/>
       <c r="G27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="28"/>
       <c r="G28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="28"/>
       <c r="G29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="28"/>
@@ -3305,99 +3544,99 @@
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="55"/>
+      <c r="C36" s="56"/>
       <c r="D36" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="55"/>
+      <c r="C37" s="56"/>
       <c r="D37" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="28"/>
       <c r="G37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="55"/>
+      <c r="C38" s="56"/>
       <c r="D38" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="28"/>
       <c r="G38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="56"/>
+      <c r="C39" s="57"/>
       <c r="D39" s="26" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="30"/>
@@ -3406,57 +3645,57 @@
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="54" t="s">
-        <v>200</v>
+      <c r="C40" s="55" t="s">
+        <v>198</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E40" s="40"/>
       <c r="F40" s="41">
         <v>1200</v>
       </c>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="43"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="55"/>
+      <c r="C41" s="56"/>
       <c r="D41" s="26" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="27"/>
       <c r="F41" s="30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="44"/>
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="55"/>
+      <c r="C42" s="56"/>
       <c r="D42" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G42" s="27"/>
       <c r="H42" s="44"/>
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="55"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F43" s="30"/>
       <c r="G43" s="27"/>
@@ -3464,12 +3703,12 @@
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="56"/>
+      <c r="C44" s="57"/>
       <c r="D44" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="27"/>
@@ -3477,11 +3716,11 @@
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="54" t="s">
-        <v>201</v>
+      <c r="C45" s="55" t="s">
+        <v>199</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
@@ -3492,12 +3731,12 @@
       <c r="I45" s="43"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="55"/>
+      <c r="C46" s="56"/>
       <c r="D46" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="27"/>
@@ -3505,24 +3744,24 @@
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="55"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G47" s="27"/>
       <c r="H47" s="44"/>
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="55"/>
+      <c r="C48" s="56"/>
       <c r="D48" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E48" s="27"/>
       <c r="F48" s="28"/>
@@ -3531,73 +3770,73 @@
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="55"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E49" s="27"/>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="55"/>
+      <c r="C50" s="56"/>
       <c r="D50" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="28"/>
       <c r="G50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I50" s="29"/>
     </row>
     <row r="51" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="55"/>
+      <c r="C51" s="56"/>
       <c r="D51" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="28"/>
       <c r="G51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I51" s="29"/>
     </row>
     <row r="52" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="55"/>
+      <c r="C52" s="56"/>
       <c r="D52" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
       <c r="G52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H52" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="56"/>
+      <c r="C53" s="57"/>
       <c r="D53" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E53" s="34"/>
       <c r="F53" s="35" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G53" s="34"/>
       <c r="H53" s="45"/>
@@ -3686,13 +3925,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -3704,13 +3943,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3718,13 +3957,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>202</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -3734,14 +3973,14 @@
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>212</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="30"/>
@@ -3750,54 +3989,54 @@
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" t="s">
         <v>181</v>
-      </c>
-      <c r="E5" t="s">
-        <v>183</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F6" s="28"/>
       <c r="G6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E7" s="27"/>
       <c r="F7" s="30"/>
@@ -3806,8 +4045,8 @@
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="54" t="s">
-        <v>205</v>
+      <c r="C8" s="55" t="s">
+        <v>203</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>1</v>
@@ -3819,86 +4058,86 @@
       <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="28"/>
       <c r="G9" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I9" s="29"/>
       <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="28"/>
       <c r="G10" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="55"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="28"/>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s">
         <v>140</v>
-      </c>
-      <c r="E14" t="s">
-        <v>142</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" s="27"/>
@@ -3906,35 +4145,35 @@
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H15" s="51"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H16" s="51"/>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
@@ -3943,135 +4182,135 @@
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
         <v>163</v>
-      </c>
-      <c r="E20" t="s">
-        <v>165</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" t="s">
         <v>163</v>
-      </c>
-      <c r="E21" t="s">
-        <v>165</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H22" s="44"/>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="28"/>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="56"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="52"/>
       <c r="G25" s="53" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I25" s="36"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="54" t="s">
-        <v>206</v>
+      <c r="C26" s="55" t="s">
+        <v>204</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -4082,9 +4321,9 @@
       <c r="I26" s="43"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="56"/>
+      <c r="C27" s="57"/>
       <c r="D27" s="33" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="52"/>
@@ -4093,11 +4332,11 @@
       <c r="I27" s="36"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="54" t="s">
-        <v>201</v>
+      <c r="C28" s="55" t="s">
+        <v>199</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>9</v>
@@ -4108,12 +4347,12 @@
       <c r="I28" s="43"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F29" s="28"/>
       <c r="G29" s="27"/>
@@ -4121,9 +4360,9 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="28"/>
@@ -4132,9 +4371,9 @@
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
@@ -4143,73 +4382,73 @@
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="28"/>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="56"/>
+      <c r="C36" s="57"/>
       <c r="D36" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G36" s="34"/>
       <c r="H36" s="45"/>
@@ -4280,13 +4519,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -4298,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4312,13 +4551,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>210</v>
+        <v>207</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>208</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -4328,44 +4567,44 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="55"/>
+        <v>212</v>
+      </c>
+      <c r="C3" s="56"/>
       <c r="D3" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="28"/>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="28"/>
@@ -4374,9 +4613,9 @@
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="30"/>
@@ -4385,54 +4624,54 @@
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="55"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H7" s="44"/>
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" t="s">
         <v>181</v>
-      </c>
-      <c r="E8" t="s">
-        <v>183</v>
       </c>
       <c r="F8" s="28"/>
       <c r="G8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H8" s="44"/>
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="55"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F9" s="28"/>
       <c r="G9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H9" s="44"/>
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="55"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="30"/>
@@ -4441,9 +4680,9 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="56"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="52"/>
@@ -4452,280 +4691,280 @@
       <c r="I11" s="36"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="54" t="s">
-        <v>205</v>
+      <c r="C12" s="55" t="s">
+        <v>203</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H12" s="42"/>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="55"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="55"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="55"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="55"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="55"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F17" s="28"/>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="55"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="55"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="55"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="55"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="55"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="28"/>
       <c r="G22" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="55"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="28"/>
       <c r="G23" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I23" s="29"/>
+    </row>
+    <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="56"/>
+      <c r="D24" s="26" t="s">
         <v>170</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="29"/>
-    </row>
-    <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="55"/>
-      <c r="D24" s="26" t="s">
-        <v>172</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="56"/>
+      <c r="D25" s="26" t="s">
         <v>170</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="29"/>
-    </row>
-    <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="55"/>
-      <c r="D25" s="26" t="s">
-        <v>172</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="28"/>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="55"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="26" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="28"/>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H28" s="44"/>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="55"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="28"/>
@@ -4734,348 +4973,348 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="55"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F30" s="28"/>
       <c r="G30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="55"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="55"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" t="s">
         <v>163</v>
-      </c>
-      <c r="E32" t="s">
-        <v>165</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="55"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E33" t="s">
         <v>163</v>
-      </c>
-      <c r="E33" t="s">
-        <v>165</v>
       </c>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="55"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="55"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="55"/>
+      <c r="C36" s="56"/>
       <c r="D36" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="55"/>
+      <c r="C37" s="56"/>
       <c r="D37" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="28"/>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="55"/>
+      <c r="C38" s="56"/>
       <c r="D38" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="28"/>
       <c r="G38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="55"/>
+      <c r="C39" s="56"/>
       <c r="D39" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="55"/>
+      <c r="C40" s="56"/>
       <c r="D40" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I40" s="29"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="55"/>
+      <c r="C41" s="56"/>
       <c r="D41" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F41" s="28"/>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="55"/>
+      <c r="C42" s="56"/>
       <c r="D42" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F42" s="28"/>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="55"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="55"/>
+      <c r="C44" s="56"/>
       <c r="D44" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H44" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="55"/>
+      <c r="C45" s="56"/>
       <c r="D45" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I45" s="29"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="55"/>
+      <c r="C46" s="56"/>
       <c r="D46" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" t="s">
         <v>160</v>
-      </c>
-      <c r="E46" t="s">
-        <v>162</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="55"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E47" t="s">
         <v>160</v>
-      </c>
-      <c r="E47" t="s">
-        <v>162</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="55"/>
+      <c r="C48" s="56"/>
       <c r="D48" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F48" s="28"/>
       <c r="G48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H48" s="44"/>
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="55"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H49" s="44"/>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="56"/>
+      <c r="C50" s="57"/>
       <c r="D50" s="33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="52"/>
       <c r="G50" s="53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H50" s="45"/>
       <c r="I50" s="36"/>
     </row>
     <row r="51" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="57" t="s">
-        <v>206</v>
+      <c r="C51" s="58" t="s">
+        <v>204</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>5</v>
@@ -5086,9 +5325,9 @@
       <c r="I51" s="43"/>
     </row>
     <row r="52" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="58"/>
+      <c r="C52" s="59"/>
       <c r="D52" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
@@ -5097,11 +5336,11 @@
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="54" t="s">
-        <v>201</v>
+      <c r="C53" s="55" t="s">
+        <v>199</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>9</v>
@@ -5112,12 +5351,12 @@
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="55"/>
+      <c r="C54" s="56"/>
       <c r="D54" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F54" s="28"/>
       <c r="G54" s="27"/>
@@ -5125,9 +5364,9 @@
       <c r="I54" s="29"/>
     </row>
     <row r="55" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="55"/>
+      <c r="C55" s="56"/>
       <c r="D55" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="28"/>
@@ -5136,9 +5375,9 @@
       <c r="I55" s="29"/>
     </row>
     <row r="56" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="55"/>
+      <c r="C56" s="56"/>
       <c r="D56" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E56" s="27"/>
       <c r="F56" s="28"/>
@@ -5147,73 +5386,73 @@
       <c r="I56" s="29"/>
     </row>
     <row r="57" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="55"/>
+      <c r="C57" s="56"/>
       <c r="D57" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="28"/>
       <c r="G57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I57" s="29"/>
     </row>
     <row r="58" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="55"/>
+      <c r="C58" s="56"/>
       <c r="D58" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="28"/>
       <c r="G58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H58" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I58" s="29"/>
     </row>
     <row r="59" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="55"/>
+      <c r="C59" s="56"/>
       <c r="D59" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E59" s="27"/>
       <c r="F59" s="28"/>
       <c r="G59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H59" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I59" s="29"/>
     </row>
     <row r="60" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="55"/>
+      <c r="C60" s="56"/>
       <c r="D60" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="28"/>
       <c r="G60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H60" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I60" s="29"/>
     </row>
     <row r="61" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="56"/>
+      <c r="C61" s="57"/>
       <c r="D61" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="35" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G61" s="34"/>
       <c r="H61" s="45"/>
@@ -5276,10 +5515,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="23" t="s">
         <v>2</v>
@@ -5291,13 +5530,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -5305,7 +5544,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>12</v>
@@ -5318,13 +5557,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="30"/>
@@ -5334,35 +5573,35 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H4" s="29"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="28"/>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C6" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="30"/>
@@ -5377,122 +5616,122 @@
       <c r="D7" s="37"/>
       <c r="E7" s="28"/>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="27"/>
       <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="28"/>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="28"/>
       <c r="F9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G10" s="27"/>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G11" s="27"/>
       <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="28"/>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C13" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="28"/>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C14" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="28"/>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C15" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C16" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -5504,10 +5743,10 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
@@ -5516,22 +5755,22 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="28"/>
       <c r="F18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G18" s="27"/>
       <c r="H18" s="29"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" t="s">
         <v>140</v>
-      </c>
-      <c r="D19" t="s">
-        <v>142</v>
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
@@ -5540,12 +5779,12 @@
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C20" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="28"/>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G20" s="27"/>
       <c r="H20" s="29"/>
@@ -5557,54 +5796,54 @@
       <c r="D21" s="27"/>
       <c r="E21" s="28"/>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G21" s="27"/>
       <c r="H21" s="29"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C22" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G22" s="27"/>
       <c r="H22" s="29"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C23" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C24" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="28"/>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G24" s="27"/>
       <c r="H24" s="29"/>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C25" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="28"/>
@@ -5614,7 +5853,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C26" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="28"/>
@@ -5624,7 +5863,7 @@
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C27" s="26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="31"/>
@@ -5634,275 +5873,275 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C28" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="28"/>
       <c r="F28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C29" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="28"/>
       <c r="F29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C30" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="28"/>
       <c r="F30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C31" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="28"/>
       <c r="F31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C32" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="28"/>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H32" s="29"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C33" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="28"/>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H33" s="29"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C34" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D34" s="27"/>
       <c r="E34" s="28"/>
       <c r="F34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H34" s="29"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C35" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
       <c r="F35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C36" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" s="32"/>
       <c r="E36" s="28"/>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H36" s="29"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C37" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" s="32"/>
       <c r="E37" s="28"/>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H37" s="29"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C38" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H38" s="29"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C39" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E39" s="28"/>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H39" s="29"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C40" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" t="s">
         <v>160</v>
-      </c>
-      <c r="D40" t="s">
-        <v>162</v>
       </c>
       <c r="E40" s="28"/>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H40" s="29"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C41" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" t="s">
         <v>160</v>
-      </c>
-      <c r="D41" t="s">
-        <v>162</v>
       </c>
       <c r="E41" s="28"/>
       <c r="F41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H41" s="29"/>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C42" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E42" s="28"/>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H42" s="29"/>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C43" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E43" s="28"/>
       <c r="F43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H43" s="29"/>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C44" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" t="s">
         <v>163</v>
-      </c>
-      <c r="D44" t="s">
-        <v>165</v>
       </c>
       <c r="E44" s="28"/>
       <c r="F44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H44" s="29"/>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C45" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" t="s">
         <v>163</v>
-      </c>
-      <c r="D45" t="s">
-        <v>165</v>
       </c>
       <c r="E45" s="28"/>
       <c r="F45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H45" s="29"/>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C46" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="28"/>
@@ -5912,185 +6151,185 @@
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C47" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E47" s="28"/>
       <c r="F47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G47" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H47" s="29"/>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C48" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E48" s="28"/>
       <c r="F48" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G48" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H48" s="29"/>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C49" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E49" s="28"/>
       <c r="F49" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H49" s="29"/>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C50" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E50" s="28"/>
       <c r="F50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G50" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H50" s="29"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C51" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E51" s="28"/>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H51" s="29"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C52" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E52" s="28"/>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H52" s="29"/>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C53" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H53" s="29"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C54" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E54" s="28"/>
       <c r="F54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H54" s="29"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C55" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D55" s="32"/>
       <c r="E55" s="28"/>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G55" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H55" s="29"/>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C56" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D56" s="32"/>
       <c r="E56" s="28"/>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H56" s="29"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C57" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="28"/>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H57" s="29"/>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C58" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="28"/>
       <c r="F58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H58" s="29"/>
     </row>
@@ -6101,10 +6340,10 @@
       <c r="D59" s="30"/>
       <c r="E59" s="28"/>
       <c r="F59" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H59" s="29"/>
     </row>
@@ -6115,94 +6354,94 @@
       <c r="D60" s="30"/>
       <c r="E60" s="28"/>
       <c r="F60" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H60" s="29"/>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C61" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28"/>
       <c r="F61" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H61" s="29"/>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C62" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D62" s="30"/>
       <c r="E62" s="28"/>
       <c r="F62" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G62" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H62" s="29"/>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C63" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="28"/>
       <c r="F63" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H63" s="29"/>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C64" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="28"/>
       <c r="F64" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G64" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H64" s="29"/>
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C65" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D65" s="27"/>
       <c r="E65" s="28"/>
       <c r="F65" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G65" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H65" s="29"/>
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C66" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="28"/>
       <c r="F66" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G66" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H66" s="29"/>
     </row>
@@ -6228,74 +6467,74 @@
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C69" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E69" s="28"/>
       <c r="F69" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G69" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H69" s="29"/>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C70" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E70" s="28"/>
       <c r="F70" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H70" s="29"/>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C71" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D71" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G71" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H71" s="29"/>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C72" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E72" s="28"/>
       <c r="F72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H72" s="29"/>
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C73" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E73" s="28"/>
       <c r="F73" s="27"/>
@@ -6304,7 +6543,7 @@
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C74" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="28"/>
@@ -6314,35 +6553,35 @@
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C75" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="28"/>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G75" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H75" s="29"/>
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C76" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="28"/>
       <c r="F76" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G76" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H76" s="29"/>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C77" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="28"/>
@@ -6352,19 +6591,19 @@
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C78" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D78" s="32"/>
       <c r="E78" s="28"/>
       <c r="F78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G78" s="27"/>
       <c r="H78" s="29"/>
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C79" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="28"/>
@@ -6374,7 +6613,7 @@
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C80" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="30"/>
@@ -6384,49 +6623,49 @@
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C81" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G81" s="27"/>
       <c r="H81" s="29"/>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C82" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D82" t="s">
         <v>181</v>
-      </c>
-      <c r="D82" t="s">
-        <v>183</v>
       </c>
       <c r="E82" s="28"/>
       <c r="F82" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G82" s="27"/>
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C83" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G83" s="27"/>
       <c r="H83" s="29"/>
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C84" s="26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="30"/>
@@ -6439,7 +6678,7 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E85" s="30"/>
       <c r="F85" s="27"/>
@@ -6451,7 +6690,7 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="27"/>
@@ -6463,7 +6702,7 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="27"/>
@@ -6472,7 +6711,7 @@
     </row>
     <row r="88" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C88" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="28"/>
@@ -6482,19 +6721,19 @@
     </row>
     <row r="89" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C89" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="59"/>
+      <c r="E89" s="54"/>
       <c r="F89" s="27"/>
       <c r="G89" s="27"/>
       <c r="H89" s="29"/>
     </row>
     <row r="90" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C90" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="28"/>
@@ -6509,10 +6748,10 @@
       <c r="D91" s="27"/>
       <c r="E91" s="28"/>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G91" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H91" s="29"/>
     </row>
@@ -6523,66 +6762,66 @@
       <c r="D92" s="27"/>
       <c r="E92" s="28"/>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G92" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H92" s="29"/>
     </row>
     <row r="93" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C93" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="28"/>
       <c r="F93" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H93" s="29"/>
     </row>
     <row r="94" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C94" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="28"/>
       <c r="F94" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C95" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="28"/>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G95" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C96" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="28"/>
       <c r="F96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H96" s="29"/>
     </row>
@@ -6608,59 +6847,59 @@
     </row>
     <row r="99" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C99" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D99" s="27"/>
       <c r="E99" s="28"/>
       <c r="F99" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G99" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C100" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="28"/>
       <c r="F100" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G100" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C101" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D101" s="30"/>
       <c r="E101" s="28"/>
       <c r="F101" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C102" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D102" s="30"/>
       <c r="E102" s="28"/>
       <c r="F102" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C103" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D103" s="34"/>
       <c r="E103" s="35"/>
@@ -6757,16 +6996,16 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -6778,53 +7017,53 @@
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" t="str">
         <f>_xlfn.XLOOKUP(B2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>C[N+](C)(CCCNS(=O)(=O)CCC(C(C(C(C(C(F)(F)F)(F)F)(F)F)(F)F)(F)F)(F)F)[O-]</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>1.2</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2">
         <v>0.99760000000000004</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -6833,33 +7072,33 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" t="str">
         <f>_xlfn.XLOOKUP(B3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN(C)C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F3">
         <v>11.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3">
         <v>0.90400000000000003</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -6868,10 +7107,10 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="str">
         <f>_xlfn.XLOOKUP(B4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6881,7 +7120,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -6890,10 +7129,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" t="str">
         <f>_xlfn.XLOOKUP(B5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6903,7 +7142,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="J5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -6912,10 +7151,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="str">
         <f>_xlfn.XLOOKUP(B6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6925,7 +7164,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="J6" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -6934,10 +7173,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="str">
         <f>_xlfn.XLOOKUP(B7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6947,7 +7186,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="J7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -6956,10 +7195,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" t="str">
         <f>_xlfn.XLOOKUP(B8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6969,7 +7208,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="J8" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K8" s="3">
         <v>2</v>
@@ -6978,10 +7217,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.XLOOKUP(B9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -6991,7 +7230,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="J9" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K9" s="3">
         <v>3</v>
@@ -7000,10 +7239,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" t="str">
         <f>_xlfn.XLOOKUP(B10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7014,7 +7253,7 @@
       <c r="H10" s="11"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K10" s="3">
         <v>2</v>
@@ -7023,10 +7262,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" t="str">
         <f>_xlfn.XLOOKUP(B11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7037,7 +7276,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="3">
         <v>2</v>
@@ -7046,10 +7285,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="str">
         <f>_xlfn.XLOOKUP(B12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7060,7 +7299,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K12" s="3">
         <v>2</v>
@@ -7069,10 +7308,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.XLOOKUP(B13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7083,7 +7322,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K13" s="3">
         <v>2</v>
@@ -7092,10 +7331,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.XLOOKUP(B14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7106,7 +7345,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K14" s="3">
         <v>2</v>
@@ -7115,10 +7354,10 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.XLOOKUP(B15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7129,7 +7368,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K15" s="3">
         <v>2</v>
@@ -7138,10 +7377,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16" t="str">
         <f>_xlfn.XLOOKUP(B16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7152,7 +7391,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K16" s="3">
         <v>3</v>
@@ -7161,10 +7400,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" t="str">
         <f>_xlfn.XLOOKUP(B17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7175,7 +7414,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K17" s="3">
         <v>3</v>
@@ -7184,10 +7423,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.XLOOKUP(B18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7200,7 +7439,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">

--- a/BART_FANG_2024_6-2FTNO_Example.xlsx
+++ b/BART_FANG_2024_6-2FTNO_Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\strich\Documents\BART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29208657-1433-49BF-A4AC-BEFDBEB90314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5A2F53-F1E6-46CA-8F3E-4F1A46D88211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="2" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="16440" tabRatio="857" activeTab="7" xr2:uid="{A95DC0BB-2293-4BB2-9652-B6AD234FE081}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="15" r:id="rId1"/>
@@ -24,7 +24,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="AcidityWaterSediment">#REF!</definedName>
@@ -102,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="215">
   <si>
     <t>pH</t>
   </si>
@@ -380,9 +379,6 @@
     <t>Fang, B. et al, 2024</t>
   </si>
   <si>
-    <t>Reference: 10.1021/acs.est.3c05506</t>
-  </si>
-  <si>
     <t>Tianjin, China</t>
   </si>
   <si>
@@ -695,9 +691,6 @@
     <t>Experimental Conditions</t>
   </si>
   <si>
-    <t>Phosphorous Content</t>
-  </si>
-  <si>
     <t>Compound Addition</t>
   </si>
   <si>
@@ -738,9 +731,6 @@
   </si>
   <si>
     <t>Sediment</t>
-  </si>
-  <si>
-    <t>Reference: DOI</t>
   </si>
   <si>
     <t>Test General Scenario</t>
@@ -1155,6 +1145,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1169,11 +1164,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1746,133 +1736,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Description"/>
-      <sheetName val="Compounds"/>
-      <sheetName val="Connectivity"/>
-      <sheetName val="Scenario_Sludge"/>
-      <sheetName val="Scenario_Soil"/>
-      <sheetName val="Scenario_Water-Sediment"/>
-      <sheetName val="Scenario_General"/>
-      <sheetName val="Kinetics_Confidence"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>6:2 FTAA</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCN(C)C)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>OH-6:2 FTAA</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCN(C)CO)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>6:2 FTUAA</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC/C=[N+](C)\C)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>6:2 FTSAm-SeAm</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCNC)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>6:2 FTSAm-PrA</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>6:2 FTSAm-AcAL</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC=O)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>6:2 FTSAm-AcA</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC(O)=O)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>6:2 FTSAm-ForAL</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>6:2 FTSAm</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>6:2 FTSI</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>FC(F)(C(F)(C(F)(C(F)(C(F)(C(F)(F)F)F)F)F)F)CCS(O)=O</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>6:2 FTSA</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(O)(=O)=O)F</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>6:2 FTSAm-PrAm</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>C(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)F)CS(NCCCN)(=O)=O</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -2182,7 +2045,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>49</v>
@@ -2190,50 +2053,50 @@
     </row>
     <row r="2" spans="1:2" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>112</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2345,10 +2208,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2486,7 +2349,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
@@ -2508,16 +2371,16 @@
         <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="55" t="s">
         <v>214</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>217</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>35</v>
@@ -2541,9 +2404,9 @@
         <f>_xlfn.XLOOKUP(C2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN(C)C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E2" s="61"/>
+      <c r="E2" s="56"/>
       <c r="F2">
-        <f>_xlfn.XLOOKUP(E2,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E2,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G2" s="10"/>
@@ -2563,9 +2426,9 @@
         <f>_xlfn.XLOOKUP(C3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCC/C=[N+](\C)/C)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E3" s="61"/>
+      <c r="E3" s="56"/>
       <c r="F3">
-        <f>_xlfn.XLOOKUP(E3,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E3,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G3" s="10"/>
@@ -2585,9 +2448,9 @@
         <f>_xlfn.XLOOKUP(C4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
-      <c r="E4" s="61"/>
+      <c r="E4" s="56"/>
       <c r="F4">
-        <f>_xlfn.XLOOKUP(E4,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E4,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G4" s="10"/>
@@ -2607,9 +2470,9 @@
         <f>_xlfn.XLOOKUP(C5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCNC)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E5" s="61"/>
+      <c r="E5" s="56"/>
       <c r="F5">
-        <f>_xlfn.XLOOKUP(E5,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E5,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G5" s="10"/>
@@ -2629,9 +2492,9 @@
         <f>_xlfn.XLOOKUP(C6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCNC)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E6" s="62"/>
+      <c r="E6" s="57"/>
       <c r="F6">
-        <f>_xlfn.XLOOKUP(E6,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E6,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G6" s="10"/>
@@ -2651,9 +2514,9 @@
         <f>_xlfn.XLOOKUP(C7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCCN)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E7" s="62"/>
+      <c r="E7" s="57"/>
       <c r="F7">
-        <f>_xlfn.XLOOKUP(E7,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E7,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G7" s="10"/>
@@ -2673,9 +2536,9 @@
         <f>_xlfn.XLOOKUP(C8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
-      <c r="E8" s="62"/>
+      <c r="E8" s="57"/>
       <c r="F8">
-        <f>_xlfn.XLOOKUP(E8,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E8,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G8" s="10"/>
@@ -2695,9 +2558,9 @@
         <f>_xlfn.XLOOKUP(C9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCC(O)=O)(=O)=O)F</v>
       </c>
-      <c r="E9" s="61"/>
+      <c r="E9" s="56"/>
       <c r="F9">
-        <f>_xlfn.XLOOKUP(E9,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E9,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
@@ -2719,9 +2582,9 @@
         <f>_xlfn.XLOOKUP(C10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N(C)CCC(O)=O)(=O)=O)F</v>
       </c>
-      <c r="E10" s="61"/>
+      <c r="E10" s="56"/>
       <c r="F10">
-        <f>_xlfn.XLOOKUP(E10,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E10,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G10" s="10"/>
@@ -2741,9 +2604,9 @@
         <f>_xlfn.XLOOKUP(C11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E11" s="62"/>
+      <c r="E11" s="57"/>
       <c r="F11">
-        <f>_xlfn.XLOOKUP(E11,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E11,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G11" s="10"/>
@@ -2763,9 +2626,9 @@
         <f>_xlfn.XLOOKUP(C12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCC)(=O)=O)F</v>
       </c>
-      <c r="E12" s="62"/>
+      <c r="E12" s="57"/>
       <c r="F12">
-        <f>_xlfn.XLOOKUP(E12,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E12,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G12" s="10"/>
@@ -2785,9 +2648,9 @@
         <f>_xlfn.XLOOKUP(C13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCCO)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E13" s="62"/>
+      <c r="E13" s="57"/>
       <c r="F13">
-        <f>_xlfn.XLOOKUP(E13,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E13,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G13" s="10"/>
@@ -2807,9 +2670,9 @@
         <f>_xlfn.XLOOKUP(C14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E14" s="62"/>
+      <c r="E14" s="57"/>
       <c r="F14">
-        <f>_xlfn.XLOOKUP(E14,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E14,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G14" s="10"/>
@@ -2829,9 +2692,9 @@
         <f>_xlfn.XLOOKUP(C15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(C(F)(C(F)(C(F)(C(F)(C(F)(CCS(NCC(O)=O)(=O)=O)F)F)F)F)F)(F)F</v>
       </c>
-      <c r="E15" s="62"/>
+      <c r="E15" s="57"/>
       <c r="F15">
-        <f>_xlfn.XLOOKUP(E15,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E15,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G15" s="10"/>
@@ -2851,9 +2714,9 @@
         <f>_xlfn.XLOOKUP(C16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
       </c>
-      <c r="E16" s="62"/>
+      <c r="E16" s="57"/>
       <c r="F16">
-        <f>_xlfn.XLOOKUP(E16,[2]Compounds!$B$2:$B$21,[2]Compounds!$C$2:$C$21)</f>
+        <f>_xlfn.XLOOKUP(E16,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>0</v>
       </c>
       <c r="G16" s="10"/>
@@ -2873,7 +2736,11 @@
         <f>_xlfn.XLOOKUP(C17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E17" s="62"/>
+      <c r="E17" s="57"/>
+      <c r="F17">
+        <f>_xlfn.XLOOKUP(E17,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2891,7 +2758,11 @@
         <f>_xlfn.XLOOKUP(C18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)C(C)CC)=O)(=O)=O)F</v>
       </c>
-      <c r="E18" s="62"/>
+      <c r="E18" s="57"/>
+      <c r="F18">
+        <f>_xlfn.XLOOKUP(E18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2909,7 +2780,11 @@
         <f>_xlfn.XLOOKUP(C19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC(C(N)CCC)=O)(=O)=O)F</v>
       </c>
-      <c r="E19" s="62"/>
+      <c r="E19" s="57"/>
+      <c r="F19">
+        <f>_xlfn.XLOOKUP(E19,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2927,7 +2802,11 @@
         <f>_xlfn.XLOOKUP(C20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E20" s="62"/>
+      <c r="E20" s="57"/>
+      <c r="F20">
+        <f>_xlfn.XLOOKUP(E20,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2945,7 +2824,11 @@
         <f>_xlfn.XLOOKUP(C21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NC=O)(=O)=O)F</v>
       </c>
-      <c r="E21" s="62"/>
+      <c r="E21" s="57"/>
+      <c r="F21">
+        <f>_xlfn.XLOOKUP(E21,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2963,7 +2846,11 @@
         <f>_xlfn.XLOOKUP(C22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(N)(=O)=O)F</v>
       </c>
-      <c r="E22" s="62"/>
+      <c r="E22" s="57"/>
+      <c r="F22">
+        <f>_xlfn.XLOOKUP(E22,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -2975,37 +2862,179 @@
         <v>FC(F)(C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)CCS(NCCCO)(=O)=O)F</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
         <v>FC(F)(C(C(C(C(C(CCS(=O)(=O)NCCC=O)(F)F)(F)F)(F)F)(F)F)(F)F)F</v>
       </c>
-      <c r="E23" s="62"/>
+      <c r="E23" s="57"/>
+      <c r="F23">
+        <f>_xlfn.XLOOKUP(E23,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
+        <v>0</v>
+      </c>
       <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="C24" s="9"/>
-      <c r="E24" s="62"/>
+      <c r="E24" s="57"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="C25" s="9"/>
-      <c r="E25" s="62"/>
+      <c r="E25" s="57"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
-      <c r="E26" s="62"/>
+      <c r="E26" s="57"/>
       <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="57"/>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="57"/>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="E29" s="57"/>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="E30" s="57"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="E31" s="57"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="E32" s="57"/>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="E33" s="57"/>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="E34" s="57"/>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="E35" s="57"/>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="E36" s="57"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="E37" s="57"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="E38" s="57"/>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="E39" s="57"/>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="E40" s="57"/>
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="E41" s="57"/>
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="E42" s="57"/>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="E43" s="57"/>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="E44" s="57"/>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="E45" s="57"/>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="E46" s="57"/>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="E47" s="57"/>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="E48" s="57"/>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="E49" s="57"/>
+      <c r="G49" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G49" xr:uid="{4E4B432C-3A87-4B1A-A0B5-DE103EF115B8}">
       <formula1>"multistep reaction, "</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Multistep" prompt="If the reported reaction consisted of multiple enzymatic steps, please note this here by choosing &quot;multistep reaction&quot;" sqref="G1" xr:uid="{670B067C-E023-4CDC-B74A-A2B35314F74C}"/>
@@ -3020,7 +3049,7 @@
           <x14:formula1>
             <xm:f>Compounds!$B$2:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C26 A2:A26</xm:sqref>
+          <xm:sqref>C2:C49 A2:A49</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3057,7 +3086,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -3072,7 +3101,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>
@@ -3085,15 +3114,15 @@
       <c r="B2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="55" t="s">
-        <v>195</v>
+      <c r="C2" s="58" t="s">
+        <v>194</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="42"/>
@@ -3103,49 +3132,50 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="56"/>
+      <c r="B3" s="7" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: 10.1021/acs.est.3c05506</v>
+      </c>
+      <c r="C3" s="59"/>
       <c r="D3" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="27"/>
       <c r="H3" s="44"/>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="26" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="44"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56"/>
+      <c r="C5" s="59"/>
       <c r="D5" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" s="27"/>
       <c r="H5" s="44"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57"/>
+      <c r="C6" s="60"/>
       <c r="D6" s="26" t="s">
         <v>25</v>
       </c>
@@ -3158,14 +3188,14 @@
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="55" t="s">
-        <v>196</v>
+      <c r="C7" s="58" t="s">
+        <v>195</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F7" s="41">
         <v>100</v>
@@ -3177,7 +3207,7 @@
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="56"/>
+      <c r="C8" s="59"/>
       <c r="D8" s="26" t="s">
         <v>18</v>
       </c>
@@ -3192,22 +3222,22 @@
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="56"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="26" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="27"/>
       <c r="F9" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="44"/>
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="56"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="28"/>
@@ -3216,90 +3246,90 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="56"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" t="s">
         <v>161</v>
-      </c>
-      <c r="E11" t="s">
-        <v>162</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="56"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" t="s">
         <v>161</v>
-      </c>
-      <c r="E12" t="s">
-        <v>162</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="56"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="56"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="56"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H15" s="44"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="56"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="28"/>
@@ -3307,14 +3337,14 @@
         <v>46</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="56"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
@@ -3322,12 +3352,12 @@
         <v>46</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="56"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="26" t="s">
         <v>27</v>
       </c>
@@ -3337,12 +3367,12 @@
         <v>46</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="56"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="26" t="s">
         <v>27</v>
       </c>
@@ -3352,12 +3382,12 @@
         <v>46</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="56"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="26" t="s">
         <v>1</v>
       </c>
@@ -3370,20 +3400,20 @@
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="56"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="26" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G21" s="27"/>
       <c r="H21" s="44"/>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="56"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="26" t="s">
         <v>6</v>
       </c>
@@ -3393,12 +3423,12 @@
         <v>45</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="56"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="26" t="s">
         <v>6</v>
       </c>
@@ -3408,42 +3438,42 @@
         <v>45</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="56"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="56"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="56"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="26" t="s">
         <v>32</v>
       </c>
@@ -3453,12 +3483,12 @@
         <v>42</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="56"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="26" t="s">
         <v>32</v>
       </c>
@@ -3468,12 +3498,12 @@
         <v>42</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="56"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="26" t="s">
         <v>36</v>
       </c>
@@ -3483,12 +3513,12 @@
         <v>42</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="56"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="26" t="s">
         <v>36</v>
       </c>
@@ -3498,14 +3528,14 @@
         <v>42</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="56"/>
+      <c r="C30" s="59"/>
       <c r="D30" s="26" t="s">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
@@ -3513,14 +3543,14 @@
         <v>42</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="56"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="26" t="s">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
@@ -3528,12 +3558,12 @@
         <v>42</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="56"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="26" t="s">
         <v>26</v>
       </c>
@@ -3544,67 +3574,67 @@
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="56"/>
+      <c r="C33" s="59"/>
       <c r="D33" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="56"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="56"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="26" t="s">
         <v>21</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="56"/>
+      <c r="C36" s="59"/>
       <c r="D36" s="26" t="s">
         <v>21</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="56"/>
+      <c r="C37" s="59"/>
       <c r="D37" s="26" t="s">
         <v>22</v>
       </c>
@@ -3614,12 +3644,12 @@
         <v>42</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="56"/>
+      <c r="C38" s="59"/>
       <c r="D38" s="26" t="s">
         <v>22</v>
       </c>
@@ -3629,14 +3659,14 @@
         <v>42</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="57"/>
+      <c r="C39" s="60"/>
       <c r="D39" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="30"/>
@@ -3645,8 +3675,8 @@
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="55" t="s">
-        <v>198</v>
+      <c r="C40" s="58" t="s">
+        <v>196</v>
       </c>
       <c r="D40" s="39" t="s">
         <v>23</v>
@@ -3662,25 +3692,25 @@
       <c r="I40" s="43"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="56"/>
+      <c r="C41" s="59"/>
       <c r="D41" s="26" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="27"/>
       <c r="F41" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="44"/>
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="56"/>
+      <c r="C42" s="59"/>
       <c r="D42" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F42" s="30" t="s">
         <v>52</v>
@@ -3690,12 +3720,12 @@
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="56"/>
+      <c r="C43" s="59"/>
       <c r="D43" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F43" s="30"/>
       <c r="G43" s="27"/>
@@ -3703,12 +3733,12 @@
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="57"/>
+      <c r="C44" s="60"/>
       <c r="D44" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="27"/>
@@ -3716,11 +3746,11 @@
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="55" t="s">
-        <v>199</v>
+      <c r="C45" s="58" t="s">
+        <v>197</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
@@ -3731,12 +3761,12 @@
       <c r="I45" s="43"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="56"/>
+      <c r="C46" s="59"/>
       <c r="D46" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s">
         <v>136</v>
-      </c>
-      <c r="E46" t="s">
-        <v>137</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" s="27"/>
@@ -3744,24 +3774,24 @@
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="56"/>
+      <c r="C47" s="59"/>
       <c r="D47" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G47" s="27"/>
       <c r="H47" s="44"/>
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="56"/>
+      <c r="C48" s="59"/>
       <c r="D48" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" s="27"/>
       <c r="F48" s="28"/>
@@ -3770,7 +3800,7 @@
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="56"/>
+      <c r="C49" s="59"/>
       <c r="D49" s="26" t="s">
         <v>24</v>
       </c>
@@ -3780,12 +3810,12 @@
         <v>44</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="56"/>
+      <c r="C50" s="59"/>
       <c r="D50" s="26" t="s">
         <v>24</v>
       </c>
@@ -3795,14 +3825,14 @@
         <v>44</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I50" s="29"/>
     </row>
     <row r="51" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="56"/>
+      <c r="C51" s="59"/>
       <c r="D51" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="28"/>
@@ -3810,14 +3840,14 @@
         <v>44</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I51" s="29"/>
     </row>
     <row r="52" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="56"/>
+      <c r="C52" s="59"/>
       <c r="D52" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
@@ -3825,18 +3855,18 @@
         <v>44</v>
       </c>
       <c r="H52" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="57"/>
+      <c r="C53" s="60"/>
       <c r="D53" s="33" t="s">
         <v>47</v>
       </c>
       <c r="E53" s="34"/>
       <c r="F53" s="35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G53" s="34"/>
       <c r="H53" s="45"/>
@@ -3931,7 +3961,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -3946,7 +3976,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I1" s="48" t="s">
         <v>38</v>
@@ -3957,13 +3987,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>200</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -3975,12 +4005,13 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="56"/>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: 10.1021/acs.est.3c05506</v>
+      </c>
+      <c r="C3" s="59"/>
       <c r="D3" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="30"/>
@@ -3989,54 +4020,54 @@
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" t="s">
         <v>179</v>
-      </c>
-      <c r="E4" t="s">
-        <v>180</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56"/>
+      <c r="C5" s="59"/>
       <c r="D5" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="56"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F6" s="28"/>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="57"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E7" s="27"/>
       <c r="F7" s="30"/>
@@ -4045,8 +4076,8 @@
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="55" t="s">
-        <v>203</v>
+      <c r="C8" s="58" t="s">
+        <v>201</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>1</v>
@@ -4058,38 +4089,38 @@
       <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="56"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="28"/>
       <c r="G9" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I9" s="29"/>
       <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="56"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="28"/>
       <c r="G10" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="56"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="26" t="s">
         <v>6</v>
       </c>
@@ -4099,12 +4130,12 @@
         <v>45</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="56"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="26" t="s">
         <v>6</v>
       </c>
@@ -4114,30 +4145,30 @@
         <v>45</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="56"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="56"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" s="27"/>
@@ -4145,35 +4176,35 @@
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="56"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H15" s="51"/>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="56"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H16" s="51"/>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="56"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="28"/>
@@ -4182,135 +4213,135 @@
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="56"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" t="s">
         <v>161</v>
-      </c>
-      <c r="E18" t="s">
-        <v>162</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="56"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" t="s">
         <v>161</v>
-      </c>
-      <c r="E19" t="s">
-        <v>162</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="56"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="56"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="56"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" s="44"/>
       <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="56"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28"/>
       <c r="G23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="56"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="28"/>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="57"/>
+      <c r="C25" s="60"/>
       <c r="D25" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="52"/>
       <c r="G25" s="53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I25" s="36"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="55" t="s">
-        <v>204</v>
+      <c r="C26" s="58" t="s">
+        <v>202</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -4321,9 +4352,9 @@
       <c r="I26" s="43"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="57"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="52"/>
@@ -4332,11 +4363,11 @@
       <c r="I27" s="36"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="55" t="s">
-        <v>199</v>
+      <c r="C28" s="58" t="s">
+        <v>197</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>9</v>
@@ -4347,12 +4378,12 @@
       <c r="I28" s="43"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="56"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
         <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>137</v>
       </c>
       <c r="F29" s="28"/>
       <c r="G29" s="27"/>
@@ -4360,9 +4391,9 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="56"/>
+      <c r="C30" s="59"/>
       <c r="D30" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="28"/>
@@ -4371,9 +4402,9 @@
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="56"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="28"/>
@@ -4382,7 +4413,7 @@
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="56"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="26" t="s">
         <v>24</v>
       </c>
@@ -4392,12 +4423,12 @@
         <v>44</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="56"/>
+      <c r="C33" s="59"/>
       <c r="D33" s="26" t="s">
         <v>24</v>
       </c>
@@ -4407,14 +4438,14 @@
         <v>44</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="56"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
@@ -4422,14 +4453,14 @@
         <v>44</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="56"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
@@ -4437,18 +4468,18 @@
         <v>44</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
+      <c r="C36" s="60"/>
       <c r="D36" s="33" t="s">
         <v>47</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G36" s="34"/>
       <c r="H36" s="45"/>
@@ -4507,7 +4538,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="55.5546875" customWidth="1"/>
     <col min="3" max="3" width="50.33203125" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="35.21875" customWidth="1"/>
@@ -4525,7 +4556,7 @@
         <v>49</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D1" s="47" t="s">
         <v>2</v>
@@ -4540,7 +4571,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I1" s="48" t="s">
         <v>38</v>
@@ -4551,13 +4582,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>206</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
@@ -4569,42 +4600,43 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="56"/>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: 10.1021/acs.est.3c05506</v>
+      </c>
+      <c r="C3" s="59"/>
       <c r="D3" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="28"/>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="28"/>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56"/>
+      <c r="C5" s="59"/>
       <c r="D5" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="28"/>
@@ -4613,9 +4645,9 @@
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="56"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="30"/>
@@ -4624,54 +4656,54 @@
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" t="s">
         <v>179</v>
-      </c>
-      <c r="E7" t="s">
-        <v>180</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="44"/>
       <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="56"/>
+      <c r="C8" s="59"/>
       <c r="D8" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F8" s="28"/>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="44"/>
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="56"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F9" s="28"/>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9" s="44"/>
       <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="56"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="30"/>
@@ -4680,9 +4712,9 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="57"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="52"/>
@@ -4691,235 +4723,235 @@
       <c r="I11" s="36"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="55" t="s">
-        <v>203</v>
+      <c r="C12" s="58" t="s">
+        <v>201</v>
       </c>
       <c r="D12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" s="42"/>
       <c r="I12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="56"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H13" s="44"/>
       <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="56"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" t="s">
         <v>42</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="56"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="56"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" t="s">
         <v>42</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="56"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F17" s="28"/>
       <c r="G17" t="s">
         <v>42</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="56"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="56"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I19" s="29"/>
     </row>
     <row r="20" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="56"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="29"/>
     </row>
     <row r="21" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="56"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="56"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="28"/>
       <c r="G22" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="29"/>
+    </row>
+    <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="59"/>
+      <c r="D23" s="26" t="s">
         <v>168</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="29"/>
-    </row>
-    <row r="23" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="56"/>
-      <c r="D23" s="26" t="s">
-        <v>169</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="28"/>
       <c r="G23" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I23" s="29"/>
     </row>
     <row r="24" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="56"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="56"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I25" s="29"/>
     </row>
     <row r="26" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="56"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="26" t="s">
         <v>6</v>
       </c>
@@ -4929,12 +4961,12 @@
         <v>45</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="56"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="26" t="s">
         <v>6</v>
       </c>
@@ -4944,27 +4976,27 @@
         <v>45</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="56"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H28" s="44"/>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="56"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="28"/>
@@ -4973,333 +5005,333 @@
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="56"/>
+      <c r="C30" s="59"/>
       <c r="D30" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" t="s">
         <v>161</v>
-      </c>
-      <c r="E30" t="s">
-        <v>162</v>
       </c>
       <c r="F30" s="28"/>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="56"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" t="s">
         <v>161</v>
-      </c>
-      <c r="E31" t="s">
-        <v>162</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="56"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="56"/>
+      <c r="C33" s="59"/>
       <c r="D33" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F33" s="28"/>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="56"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="28"/>
       <c r="G34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I34" s="29"/>
     </row>
     <row r="35" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="56"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="28"/>
       <c r="G35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I35" s="29"/>
     </row>
     <row r="36" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="56"/>
+      <c r="C36" s="59"/>
       <c r="D36" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="28"/>
       <c r="G36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="56"/>
+      <c r="C37" s="59"/>
       <c r="D37" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="28"/>
       <c r="G37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="56"/>
+      <c r="C38" s="59"/>
       <c r="D38" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="28"/>
       <c r="G38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="39" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="56"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="28"/>
       <c r="G39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I39" s="29"/>
     </row>
     <row r="40" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="56"/>
+      <c r="C40" s="59"/>
       <c r="D40" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I40" s="29"/>
     </row>
     <row r="41" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="56"/>
+      <c r="C41" s="59"/>
       <c r="D41" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F41" s="28"/>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I41" s="29"/>
     </row>
     <row r="42" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="56"/>
+      <c r="C42" s="59"/>
       <c r="D42" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F42" s="28"/>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I42" s="29"/>
     </row>
     <row r="43" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="56"/>
+      <c r="C43" s="59"/>
       <c r="D43" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I43" s="29"/>
     </row>
     <row r="44" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="56"/>
+      <c r="C44" s="59"/>
       <c r="D44" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" t="s">
         <v>158</v>
-      </c>
-      <c r="E44" t="s">
-        <v>159</v>
       </c>
       <c r="F44" s="28"/>
       <c r="G44" t="s">
         <v>42</v>
       </c>
       <c r="H44" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I44" s="29"/>
     </row>
     <row r="45" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="56"/>
+      <c r="C45" s="59"/>
       <c r="D45" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
         <v>158</v>
-      </c>
-      <c r="E45" t="s">
-        <v>159</v>
       </c>
       <c r="F45" s="28"/>
       <c r="G45" t="s">
         <v>42</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I45" s="29"/>
     </row>
     <row r="46" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="56"/>
+      <c r="C46" s="59"/>
       <c r="D46" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F46" s="28"/>
       <c r="G46" t="s">
         <v>42</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I46" s="29"/>
     </row>
     <row r="47" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="56"/>
+      <c r="C47" s="59"/>
       <c r="D47" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F47" s="28"/>
       <c r="G47" t="s">
         <v>42</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I47" s="29"/>
     </row>
     <row r="48" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="56"/>
+      <c r="C48" s="59"/>
       <c r="D48" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F48" s="28"/>
       <c r="G48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H48" s="44"/>
       <c r="I48" s="29"/>
     </row>
     <row r="49" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="56"/>
+      <c r="C49" s="59"/>
       <c r="D49" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H49" s="44"/>
       <c r="I49" s="29"/>
     </row>
     <row r="50" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="57"/>
+      <c r="C50" s="60"/>
       <c r="D50" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="52"/>
@@ -5310,11 +5342,11 @@
       <c r="I50" s="36"/>
     </row>
     <row r="51" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="58" t="s">
-        <v>204</v>
+      <c r="C51" s="61" t="s">
+        <v>202</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>5</v>
@@ -5325,9 +5357,9 @@
       <c r="I51" s="43"/>
     </row>
     <row r="52" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="59"/>
+      <c r="C52" s="62"/>
       <c r="D52" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="28"/>
@@ -5336,11 +5368,11 @@
       <c r="I52" s="29"/>
     </row>
     <row r="53" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="55" t="s">
-        <v>199</v>
+      <c r="C53" s="58" t="s">
+        <v>197</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>9</v>
@@ -5351,12 +5383,12 @@
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="56"/>
+      <c r="C54" s="59"/>
       <c r="D54" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" t="s">
         <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>137</v>
       </c>
       <c r="F54" s="28"/>
       <c r="G54" s="27"/>
@@ -5364,9 +5396,9 @@
       <c r="I54" s="29"/>
     </row>
     <row r="55" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="56"/>
+      <c r="C55" s="59"/>
       <c r="D55" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="28"/>
@@ -5375,9 +5407,9 @@
       <c r="I55" s="29"/>
     </row>
     <row r="56" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="56"/>
+      <c r="C56" s="59"/>
       <c r="D56" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" s="27"/>
       <c r="F56" s="28"/>
@@ -5386,7 +5418,7 @@
       <c r="I56" s="29"/>
     </row>
     <row r="57" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="56"/>
+      <c r="C57" s="59"/>
       <c r="D57" s="26" t="s">
         <v>24</v>
       </c>
@@ -5396,12 +5428,12 @@
         <v>44</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I57" s="29"/>
     </row>
     <row r="58" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="56"/>
+      <c r="C58" s="59"/>
       <c r="D58" s="26" t="s">
         <v>24</v>
       </c>
@@ -5411,14 +5443,14 @@
         <v>44</v>
       </c>
       <c r="H58" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I58" s="29"/>
     </row>
     <row r="59" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="56"/>
+      <c r="C59" s="59"/>
       <c r="D59" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E59" s="27"/>
       <c r="F59" s="28"/>
@@ -5426,14 +5458,14 @@
         <v>44</v>
       </c>
       <c r="H59" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I59" s="29"/>
     </row>
     <row r="60" spans="3:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="56"/>
+      <c r="C60" s="59"/>
       <c r="D60" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="28"/>
@@ -5441,18 +5473,18 @@
         <v>44</v>
       </c>
       <c r="H60" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I60" s="29"/>
     </row>
     <row r="61" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="57"/>
+      <c r="C61" s="60"/>
       <c r="D61" s="33" t="s">
         <v>47</v>
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="35" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G61" s="34"/>
       <c r="H61" s="45"/>
@@ -5533,7 +5565,7 @@
         <v>40</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H1" s="25" t="s">
         <v>38</v>
@@ -5544,7 +5576,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>12</v>
@@ -5559,11 +5591,12 @@
       <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>212</v>
+      <c r="B3" s="38" t="str">
+        <f>"Reference: " &amp;Description!B3</f>
+        <v>Reference: 10.1021/acs.est.3c05506</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="30"/>
@@ -5573,7 +5606,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -5581,13 +5614,13 @@
         <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H4" s="29"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="28"/>
@@ -5595,7 +5628,7 @@
         <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H5" s="29"/>
     </row>
@@ -5623,52 +5656,52 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="28"/>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="28"/>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G9" s="27"/>
       <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
         <v>129</v>
-      </c>
-      <c r="D10" t="s">
-        <v>130</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G10" s="27"/>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G11" s="27"/>
       <c r="H11" s="29"/>
@@ -5680,10 +5713,10 @@
       <c r="D12" s="27"/>
       <c r="E12" s="28"/>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H12" s="29"/>
     </row>
@@ -5694,10 +5727,10 @@
       <c r="D13" s="27"/>
       <c r="E13" s="28"/>
       <c r="F13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H13" s="29"/>
     </row>
@@ -5711,7 +5744,7 @@
         <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H14" s="29"/>
     </row>
@@ -5725,13 +5758,13 @@
         <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C16" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -5743,10 +5776,10 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" t="s">
         <v>136</v>
-      </c>
-      <c r="D17" t="s">
-        <v>137</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
@@ -5755,22 +5788,22 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D18" s="27"/>
       <c r="E18" s="28"/>
       <c r="F18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G18" s="27"/>
       <c r="H18" s="29"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
@@ -5803,35 +5836,35 @@
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C22" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" t="s">
         <v>141</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G22" s="27"/>
       <c r="H22" s="29"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C23" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C24" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="28"/>
@@ -5843,7 +5876,7 @@
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C25" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="28"/>
@@ -5853,7 +5886,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C26" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="28"/>
@@ -5863,7 +5896,7 @@
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C27" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="31"/>
@@ -5873,113 +5906,113 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C28" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="28"/>
       <c r="F28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C29" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="28"/>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C30" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="28"/>
       <c r="F30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C31" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="28"/>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C32" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="28"/>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H32" s="29"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C33" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="28"/>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H33" s="29"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C34" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D34" s="27"/>
       <c r="E34" s="28"/>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H34" s="29"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C35" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
       <c r="F35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H35" s="29"/>
     </row>
@@ -5993,7 +6026,7 @@
         <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H36" s="29"/>
     </row>
@@ -6007,141 +6040,141 @@
         <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H37" s="29"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C38" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
         <v>158</v>
-      </c>
-      <c r="D38" t="s">
-        <v>159</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" t="s">
         <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H38" s="29"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C39" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s">
         <v>158</v>
-      </c>
-      <c r="D39" t="s">
-        <v>159</v>
       </c>
       <c r="E39" s="28"/>
       <c r="F39" t="s">
         <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H39" s="29"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C40" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="28"/>
       <c r="F40" t="s">
         <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H40" s="29"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C41" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="28"/>
       <c r="F41" t="s">
         <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H41" s="29"/>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C42" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
         <v>161</v>
-      </c>
-      <c r="D42" t="s">
-        <v>162</v>
       </c>
       <c r="E42" s="28"/>
       <c r="F42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H42" s="29"/>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C43" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" t="s">
         <v>161</v>
-      </c>
-      <c r="D43" t="s">
-        <v>162</v>
       </c>
       <c r="E43" s="28"/>
       <c r="F43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H43" s="29"/>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C44" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" s="28"/>
       <c r="F44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H44" s="29"/>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C45" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E45" s="28"/>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="29"/>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C46" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="28"/>
@@ -6151,129 +6184,129 @@
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C47" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="28"/>
       <c r="F47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H47" s="29"/>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C48" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E48" s="28"/>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H48" s="29"/>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C49" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E49" s="28"/>
       <c r="F49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H49" s="29"/>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C50" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E50" s="28"/>
       <c r="F50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H50" s="29"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C51" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E51" s="28"/>
       <c r="F51" t="s">
         <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H51" s="29"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C52" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E52" s="28"/>
       <c r="F52" t="s">
         <v>42</v>
       </c>
       <c r="G52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H52" s="29"/>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C53" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" t="s">
         <v>42</v>
       </c>
       <c r="G53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H53" s="29"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C54" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E54" s="28"/>
       <c r="F54" t="s">
         <v>42</v>
       </c>
       <c r="G54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H54" s="29"/>
     </row>
@@ -6287,7 +6320,7 @@
         <v>42</v>
       </c>
       <c r="G55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H55" s="29"/>
     </row>
@@ -6301,7 +6334,7 @@
         <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H56" s="29"/>
     </row>
@@ -6315,7 +6348,7 @@
         <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H57" s="29"/>
     </row>
@@ -6329,7 +6362,7 @@
         <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H58" s="29"/>
     </row>
@@ -6340,10 +6373,10 @@
       <c r="D59" s="30"/>
       <c r="E59" s="28"/>
       <c r="F59" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H59" s="29"/>
     </row>
@@ -6354,66 +6387,66 @@
       <c r="D60" s="30"/>
       <c r="E60" s="28"/>
       <c r="F60" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H60" s="29"/>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C61" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28"/>
       <c r="F61" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H61" s="29"/>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C62" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D62" s="30"/>
       <c r="E62" s="28"/>
       <c r="F62" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H62" s="29"/>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C63" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="28"/>
       <c r="F63" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H63" s="29"/>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C64" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="28"/>
       <c r="F64" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H64" s="29"/>
     </row>
@@ -6427,7 +6460,7 @@
         <v>42</v>
       </c>
       <c r="G65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H65" s="29"/>
     </row>
@@ -6441,7 +6474,7 @@
         <v>42</v>
       </c>
       <c r="G66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H66" s="29"/>
     </row>
@@ -6467,74 +6500,74 @@
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C69" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E69" s="28"/>
       <c r="F69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H69" s="29"/>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C70" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E70" s="28"/>
       <c r="F70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H70" s="29"/>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C71" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D71" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H71" s="29"/>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C72" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E72" s="28"/>
       <c r="F72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H72" s="29"/>
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C73" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E73" s="28"/>
       <c r="F73" s="27"/>
@@ -6543,7 +6576,7 @@
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C74" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="28"/>
@@ -6553,35 +6586,35 @@
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C75" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="28"/>
       <c r="F75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H75" s="29"/>
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C76" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="28"/>
       <c r="F76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G76" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H76" s="29"/>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C77" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="28"/>
@@ -6603,7 +6636,7 @@
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C79" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="28"/>
@@ -6613,7 +6646,7 @@
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C80" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="30"/>
@@ -6623,49 +6656,49 @@
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C81" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="D81" t="s">
         <v>179</v>
-      </c>
-      <c r="D81" t="s">
-        <v>180</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G81" s="27"/>
       <c r="H81" s="29"/>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C82" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D82" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E82" s="28"/>
       <c r="F82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G82" s="27"/>
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C83" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D83" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G83" s="27"/>
       <c r="H83" s="29"/>
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C84" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="30"/>
@@ -6678,7 +6711,7 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E85" s="30"/>
       <c r="F85" s="27"/>
@@ -6690,7 +6723,7 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="27"/>
@@ -6702,7 +6735,7 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="27"/>
@@ -6721,7 +6754,7 @@
     </row>
     <row r="89" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C89" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
@@ -6733,7 +6766,7 @@
     </row>
     <row r="90" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C90" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="28"/>
@@ -6751,7 +6784,7 @@
         <v>45</v>
       </c>
       <c r="G91" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H91" s="29"/>
     </row>
@@ -6765,41 +6798,41 @@
         <v>45</v>
       </c>
       <c r="G92" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H92" s="29"/>
     </row>
     <row r="93" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C93" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="28"/>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H93" s="29"/>
     </row>
     <row r="94" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C94" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="28"/>
       <c r="F94" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C95" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="28"/>
@@ -6807,13 +6840,13 @@
         <v>46</v>
       </c>
       <c r="G95" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C96" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="28"/>
@@ -6821,7 +6854,7 @@
         <v>46</v>
       </c>
       <c r="G96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H96" s="29"/>
     </row>
@@ -6855,7 +6888,7 @@
         <v>46</v>
       </c>
       <c r="G99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H99" s="29"/>
     </row>
@@ -6869,30 +6902,30 @@
         <v>46</v>
       </c>
       <c r="G100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C101" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D101" s="30"/>
       <c r="E101" s="28"/>
       <c r="F101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C102" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D102" s="30"/>
       <c r="E102" s="28"/>
       <c r="F102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="29"/>
@@ -6976,7 +7009,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.109375" customWidth="1"/>
@@ -7063,7 +7096,7 @@
         <v>0.99760000000000004</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -7098,7 +7131,7 @@
         <v>0.90400000000000003</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -7120,7 +7153,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="J4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -7142,7 +7175,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="J5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -7164,7 +7197,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="J6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -7186,7 +7219,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="J7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -7208,7 +7241,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="J8" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K8" s="3">
         <v>2</v>
@@ -7230,7 +7263,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="J9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" s="3">
         <v>3</v>
@@ -7253,7 +7286,7 @@
       <c r="H10" s="11"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K10" s="3">
         <v>2</v>
@@ -7276,7 +7309,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" s="3">
         <v>2</v>
@@ -7299,7 +7332,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" s="3">
         <v>2</v>
@@ -7322,7 +7355,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3">
         <v>2</v>
@@ -7345,7 +7378,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K14" s="3">
         <v>2</v>
@@ -7368,7 +7401,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K15" s="3">
         <v>2</v>
@@ -7391,7 +7424,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" s="3">
         <v>3</v>
@@ -7414,7 +7447,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K17" s="3">
         <v>3</v>
@@ -7426,7 +7459,7 @@
         <v>91</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.XLOOKUP(B18,Compounds!$B$2:$B$21,Compounds!$C$2:$C$21)</f>
@@ -7512,84 +7545,271 @@
       <c r="K25" s="3"/>
       <c r="L25" s="11"/>
     </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="9"/>
+      <c r="E27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="9"/>
+      <c r="E29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="9"/>
+      <c r="E30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="11"/>
+    </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="B31" s="9"/>
+      <c r="E31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="1"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="1"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" s="1"/>
+      <c r="B32" s="9"/>
+      <c r="E32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="9"/>
+      <c r="E33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="9"/>
+      <c r="E34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" s="9"/>
+      <c r="E39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B45" s="9"/>
+      <c r="E45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B48" s="9"/>
+      <c r="E48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" s="9"/>
+      <c r="E50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="9">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B32:C34 B40:B41" xr:uid="{9D9F6508-2F0E-4BCF-9953-79AD6A40D29A}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E25" xr:uid="{930A2329-8F94-46CF-AC1A-5BF5455DF29F}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E50" xr:uid="{930A2329-8F94-46CF-AC1A-5BF5455DF29F}">
       <formula1>"Half-life, Rate constant, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H25" xr:uid="{E543FE4B-6E7F-4EA1-B690-255293F334F8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H50" xr:uid="{E543FE4B-6E7F-4EA1-B690-255293F334F8}">
       <formula1>"sorption corrected, abiotic degradation corrected, sorption corrected &amp; abiotic degradation corrected, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L25" xr:uid="{975F3CE3-4F63-4C16-BA52-2318021B2EC7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L50" xr:uid="{975F3CE3-4F63-4C16-BA52-2318021B2EC7}">
       <formula1>"proposed, NA"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parameter" prompt="Reported kinetic parameter - either Half-life or Rate constant." sqref="E1" xr:uid="{F18A74F6-59D7-4E6F-8ACE-C49737E375AB}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Model" prompt="Model used to generate the kinetic parameter - i.e. &quot;first-order&quot;" sqref="D1 D4:D9" xr:uid="{F0E7BF00-EF0F-466F-B6C0-D6C929A210D5}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25" xr:uid="{18FBD4A5-6172-4673-B672-FBAFE09DD58A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G50" xr:uid="{18FBD4A5-6172-4673-B672-FBAFE09DD58A}">
       <formula1>"d, 1/d, NA"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Value Unit" prompt="Units for input kinetic parameter - usually d for Half-lives and 1/d for rate constants" sqref="G1" xr:uid="{D3E30F72-B6AE-42D0-9C59-C6C416144E46}"/>
@@ -7603,7 +7823,7 @@
           <x14:formula1>
             <xm:f>Compounds!$B$2:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B25</xm:sqref>
+          <xm:sqref>B2:B50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
